--- a/output/pdf_financials_xlsx/NEXE.xlsx
+++ b/output/pdf_financials_xlsx/NEXE.xlsx
@@ -813,16 +813,16 @@
         <v>-17.178988</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>8.339912999999999</v>
+        <v>-8.339912999999999</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>6.137065</v>
+        <v>-6.137065</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>6.530597</v>
+        <v>-6.530597</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>3.295106</v>
+        <v>-2.39536</v>
       </c>
     </row>
     <row r="17">
@@ -937,16 +937,16 @@
         <v>-17.178988</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>8.339912999999999</v>
+        <v>-8.339912999999999</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>6.137065</v>
+        <v>-6.137065</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>6.530597</v>
+        <v>-6.530597</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>2.845233</v>
+        <v>-2.845233</v>
       </c>
     </row>
     <row r="21">
@@ -1012,16 +1012,16 @@
         <v>-17.178988</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>8.339912999999999</v>
+        <v>-8.339912999999999</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>6.137065</v>
+        <v>-6.137065</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>6.530597</v>
+        <v>-6.530597</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>2.845233</v>
+        <v>-2.845233</v>
       </c>
     </row>
     <row r="24">
@@ -1087,16 +1087,16 @@
         <v>-46.429697</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>92.6657</v>
+        <v>-92.6657</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>102.284417</v>
+        <v>-102.284417</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>93.29424299999999</v>
+        <v>-93.29424299999999</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>94.8411</v>
+        <v>-94.8411</v>
       </c>
     </row>
     <row r="27">
@@ -1112,16 +1112,16 @@
         <v>-17.178988</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>8.339912999999999</v>
+        <v>-8.339912999999999</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>6.137065</v>
+        <v>-6.137065</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>6.530597</v>
+        <v>-6.530597</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>3.295106</v>
+        <v>-2.39536</v>
       </c>
     </row>
     <row r="28">
@@ -1162,16 +1162,16 @@
         <v>-16.934923</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>9.012743</v>
+        <v>-7.667083</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>7.124616</v>
+        <v>-5.149514</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>8.237105</v>
+        <v>-4.824089</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>5.071835</v>
+        <v>-0.618631</v>
       </c>
     </row>
     <row r="30">
@@ -1191,16 +1191,16 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>33397.84703179426</v>
+        <v>-28411.33550730008</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>14318.53370312312</v>
+        <v>-10349.11772981229</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>5518.480678529317</v>
+        <v>-3231.917274091543</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>1649.146623399004</v>
+        <v>-201.152684340076</v>
       </c>
     </row>
     <row r="31">
@@ -1216,16 +1216,16 @@
         <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>13.65276261218911</v>
+        <v>-18.78101830205063</v>
       </c>
     </row>
     <row r="32">
@@ -1245,16 +1245,16 @@
         </is>
       </c>
       <c r="D32" s="3" t="n">
-        <v>30904.59126954717</v>
+        <v>-30904.59126954717</v>
       </c>
       <c r="E32" s="3" t="n">
-        <v>12333.8257164677</v>
+        <v>-12333.8257164677</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>4375.19897631043</v>
+        <v>-4375.19897631043</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>925.1496538695402</v>
+        <v>-925.1496538695402</v>
       </c>
     </row>
     <row r="33">
@@ -2745,10 +2745,10 @@
         <v>8.706752</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>8.706752</v>
+        <v>11.481253</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>8.706752</v>
+        <v>12.003793</v>
       </c>
     </row>
     <row r="93">
@@ -4882,7 +4882,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>-</t>
@@ -13006,10 +13010,10 @@
         </is>
       </c>
       <c r="I199" s="5" t="n">
-        <v>6.530597</v>
+        <v>-6.530597</v>
       </c>
       <c r="J199" s="5" t="n">
-        <v>2.845233</v>
+        <v>-2.845233</v>
       </c>
     </row>
     <row r="200">
@@ -13736,13 +13740,13 @@
         </is>
       </c>
       <c r="G215" s="5" t="n">
-        <v>8.339912999999999</v>
+        <v>-8.339912999999999</v>
       </c>
       <c r="H215" s="5" t="n">
-        <v>6.137065</v>
+        <v>-6.137065</v>
       </c>
       <c r="I215" s="5" t="n">
-        <v>6.530597</v>
+        <v>-6.530597</v>
       </c>
       <c r="J215" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/NEXE.xlsx
+++ b/output/pdf_financials_xlsx/NEXE.xlsx
@@ -713,16 +713,16 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.157107</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.670913</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.547506</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.510442</v>
       </c>
     </row>
     <row r="13">
@@ -1087,16 +1087,16 @@
         <v>-46.429697</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>-92.6657</v>
+        <v>96.78307599999999</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>-102.284417</v>
+        <v>97.190636</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-93.29424299999999</v>
+        <v>97.293297</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-94.8411</v>
+        <v>97.293297</v>
       </c>
     </row>
     <row r="27">
@@ -1112,16 +1112,16 @@
         <v>-17.178988</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-8.339912999999999</v>
+        <v>-8.182805999999999</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-6.137065</v>
+        <v>-5.466152</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-6.530597</v>
+        <v>-5.983091</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-2.39536</v>
+        <v>-1.884918</v>
       </c>
     </row>
     <row r="28">
@@ -1162,16 +1162,16 @@
         <v>-16.934923</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-7.667083</v>
+        <v>-7.509976</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-5.149514</v>
+        <v>-4.478601</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-4.824089</v>
+        <v>-4.276583</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.618631</v>
+        <v>-0.108189</v>
       </c>
     </row>
     <row r="30">
@@ -1191,16 +1191,16 @@
         </is>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-28411.33550730008</v>
+        <v>-27829.15585859335</v>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-10349.11772981229</v>
+        <v>-9000.765706017122</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-3231.917274091543</v>
+        <v>-2865.113490191875</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>-201.152684340076</v>
+        <v>-35.17849536487581</v>
       </c>
     </row>
     <row r="31">
@@ -12620,7 +12620,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -13082,7 +13082,7 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -13358,7 +13358,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -13814,7 +13814,7 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -14586,7 +14586,7 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">

--- a/output/pdf_financials_xlsx/NEXE.xlsx
+++ b/output/pdf_financials_xlsx/NEXE.xlsx
@@ -930,11 +930,15 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="3" t="n">
-        <v>-2.187603</v>
-      </c>
-      <c r="C20" s="3" t="n">
-        <v>-17.178988</v>
+      <c r="B20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="D20" s="3" t="n">
         <v>-8.339912999999999</v>
@@ -956,10 +960,10 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
-        <v>0</v>
+        <v>-0.333139</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
+        <v>-0.084548</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>0</v>
@@ -16370,12 +16374,16 @@
           <t>Loss from discontinued operations $</t>
         </is>
       </c>
-      <c r="D273" t="inlineStr"/>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>NetIncomeDiscontinuousOperations</t>
+        </is>
+      </c>
       <c r="E273" s="5" t="n">
-        <v>0.333139</v>
+        <v>-0.333139</v>
       </c>
       <c r="F273" s="5" t="n">
-        <v>0.084548</v>
+        <v>-0.084548</v>
       </c>
       <c r="G273" t="inlineStr">
         <is>
